--- a/data/sensors/accelerometers.xlsx
+++ b/data/sensors/accelerometers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\react\dielcom\dielcom\data\sensors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533EC70D-3B36-4A05-910C-0B175EF9A6BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA24F8C-DCA4-454A-81B2-54831F6550A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="177">
   <si>
     <t>Brand</t>
   </si>
@@ -359,6 +359,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t>&lt;100μg/g</t>
     </r>
@@ -368,6 +370,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t>2</t>
     </r>
@@ -376,6 +380,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t>rms (50-500Hz)</t>
     </r>
@@ -453,18 +459,6 @@
     <t>1,5±0,5</t>
   </si>
   <si>
-    <t>≤60 ug/℃</t>
-  </si>
-  <si>
-    <t>≤80 (Room Temp~120℃), ≤80(120℃~150℃)</t>
-  </si>
-  <si>
-    <t>20g (20~2000Hz)</t>
-  </si>
-  <si>
-    <t>от -45 до +150</t>
-  </si>
-  <si>
     <t>≤70</t>
   </si>
   <si>
@@ -475,12 +469,6 @@
   </si>
   <si>
     <t>≤60</t>
-  </si>
-  <si>
-    <t>≤90 ug/℃</t>
-  </si>
-  <si>
-    <t>≤120 (Room Temp~120℃), ≤120(120℃~150℃)</t>
   </si>
   <si>
     <t>≤±60 ug/℃</t>
@@ -630,37 +618,51 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF4D4D4D"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -725,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -756,9 +758,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -991,7 +990,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.28515625" customWidth="1"/>
@@ -1021,103 +1020,103 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="J1" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="G1" s="15" t="s">
+      <c r="N1" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="Q1" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="T1" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="X1" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="L1" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="S1" s="16" t="s">
+      <c r="Y1" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="Z1" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB1" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="U1" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="V1" s="16" t="s">
+      <c r="AC1" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="AD1" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="X1" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y1" s="16" t="s">
+      <c r="AE1" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="AF1" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AG1" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AH1" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AI1" s="15" t="s">
         <v>176</v>
-      </c>
-      <c r="AD1" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE1" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="AF1" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG1" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="AH1" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI1" s="16" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
@@ -1125,7 +1124,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -1216,7 +1215,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
@@ -1307,7 +1306,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -1398,7 +1397,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>36</v>
@@ -1489,7 +1488,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>36</v>
@@ -1580,7 +1579,7 @@
         <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>36</v>
@@ -1671,7 +1670,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
@@ -1762,7 +1761,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>45</v>
@@ -1853,7 +1852,7 @@
         <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>59</v>
@@ -1940,7 +1939,7 @@
         <v>67</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>59</v>
@@ -2027,7 +2026,7 @@
         <v>70</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>59</v>
@@ -2114,7 +2113,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>73</v>
@@ -2205,7 +2204,7 @@
         <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>73</v>
@@ -2296,7 +2295,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>98</v>
@@ -2379,7 +2378,7 @@
         <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>98</v>
@@ -2462,7 +2461,7 @@
         <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>98</v>
@@ -2540,17 +2539,17 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="11" t="s">
         <v>129</v>
       </c>
       <c r="E18" s="2"/>
@@ -2563,37 +2562,37 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="11" t="s">
         <v>91</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="9" t="s">
-        <v>132</v>
+      <c r="P18" s="11" t="s">
+        <v>136</v>
       </c>
       <c r="Q18" s="12"/>
       <c r="R18" s="12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="S18" s="12"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-      <c r="W18" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9" t="s">
+      <c r="W18" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AB18" s="9" t="s">
-        <v>135</v>
+      <c r="AB18" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="AC18" s="2"/>
       <c r="AD18" s="6" t="s">
@@ -2604,25 +2603,25 @@
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
       <c r="AI18" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="11" t="s">
         <v>129</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>131</v>
@@ -2630,37 +2629,37 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>139</v>
+      <c r="K19" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="9" t="s">
-        <v>140</v>
+      <c r="P19" s="11" t="s">
+        <v>139</v>
       </c>
       <c r="Q19" s="12"/>
       <c r="R19" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S19" s="12"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9" t="s">
+      <c r="W19" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AB19" s="9" t="s">
-        <v>135</v>
+      <c r="AB19" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" s="6" t="s">
@@ -2671,54 +2670,54 @@
       <c r="AG19" s="2"/>
       <c r="AH19" s="2"/>
       <c r="AI19" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="13" t="s">
         <v>129</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="9" t="s">
-        <v>130</v>
+      <c r="F20" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="11" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="S20" s="13"/>
+      <c r="S20" s="12"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="11" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
@@ -2727,7 +2726,7 @@
         <v>83</v>
       </c>
       <c r="AB20" s="11" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" s="6" t="s">
@@ -2737,142 +2736,8 @@
       <c r="AF20" s="2"/>
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
-      <c r="AI20" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="11" t="s">
+      <c r="AI20" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="S21" s="13"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB21" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
-      <c r="AG21" s="2"/>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="S22" s="13"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB22" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC22" s="2"/>
-      <c r="AD22" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="2"/>
-      <c r="AG22" s="2"/>
-      <c r="AH22" s="2"/>
-      <c r="AI22" s="11" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
